--- a/evals/results/results_mock_regression.xlsx
+++ b/evals/results/results_mock_regression.xlsx
@@ -981,7 +981,7 @@
       </c>
       <c r="B1" t="inlineStr">
         <is>
-          <t>2026-07-08T07:23:42.746425+00:00</t>
+          <t>2026-07-09T05:28:47.995977+00:00</t>
         </is>
       </c>
     </row>
